--- a/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
+++ b/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:C91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.41</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="4">
@@ -531,11 +531,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fractal_breakout</t>
+          <t>kst</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>42.68</v>
+        <v>41.53</v>
       </c>
     </row>
     <row r="9">
@@ -546,11 +546,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>kst</t>
+          <t>chandelier</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>41.53</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
@@ -561,11 +561,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>chandelier</t>
+          <t>two_ma</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38.5</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37.44</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="12">
@@ -591,11 +591,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>two_ma</t>
+          <t>macd</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>36.8</v>
+        <v>33.77</v>
       </c>
     </row>
     <row r="13">
@@ -606,11 +606,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chaikin_vol</t>
+          <t>rsi_divergence</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>33.92</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="14">
@@ -621,11 +621,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>macd</t>
+          <t>schaff_trend</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33.77</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="15">
@@ -636,11 +636,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rsi_divergence</t>
+          <t>hist_vol</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32.51</v>
+        <v>30.15</v>
       </c>
     </row>
     <row r="16">
@@ -651,11 +651,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hist_vol</t>
+          <t>hp_filter_ma</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30.15</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="17">
@@ -666,11 +666,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>schaff_trend</t>
+          <t>chaikin_vol</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29.29</v>
+        <v>27.97</v>
       </c>
     </row>
     <row r="18">
@@ -741,11 +741,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true_range_ema</t>
+          <t>awesome_oscillator</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.66</v>
+        <v>23.74</v>
       </c>
     </row>
     <row r="23">
@@ -756,11 +756,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>awesome_oscillator</t>
+          <t>true_range_ema</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.74</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="24">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20.53</v>
+        <v>21.09</v>
       </c>
     </row>
     <row r="26">
@@ -981,11 +981,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>natr</t>
+          <t>fractal_breakout</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.02</v>
+        <v>8.06</v>
       </c>
     </row>
     <row r="39">
@@ -996,11 +996,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eom</t>
+          <t>rsi</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7.46</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>obv_ma</t>
+          <t>eom</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>6.88</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="41">
@@ -1026,11 +1026,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>trend_intensity</t>
+          <t>natr</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.78</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="42">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>marubozu</t>
+          <t>obv_ma</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5.5</v>
+        <v>6.88</v>
       </c>
     </row>
     <row r="43">
@@ -1056,11 +1056,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dpo</t>
+          <t>trend_intensity</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.41</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="44">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>supertrend_rsi</t>
+          <t>marubozu</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.4</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="45">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>williams_r</t>
+          <t>dpo</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2.95</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="46">
@@ -1101,11 +1101,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>bollinger</t>
+          <t>supertrend_rsi</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2.83</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="47">
@@ -1116,11 +1116,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>rsi</t>
+          <t>williams_r</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.29</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="48">
@@ -1296,11 +1296,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ibs</t>
+          <t>doji_reversal</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-2.88</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="60">
@@ -1311,11 +1311,11 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ichimoku_rsi</t>
+          <t>ibs</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-3.01</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="61">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>std_channel</t>
+          <t>ichimoku_rsi</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-3.69</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="62">
@@ -1341,11 +1341,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ppo</t>
+          <t>std_channel</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-3.75</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="63">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>stochastic</t>
+          <t>ppo</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-4.36</v>
+        <v>-4.14</v>
       </c>
     </row>
     <row r="64">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>tsi</t>
+          <t>stochastic</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-5.08</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="65">
@@ -1386,11 +1386,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>vpt</t>
+          <t>tsi</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-5.28</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="66">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>mean_reversion</t>
+          <t>vpt</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-5.65</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="67">
@@ -1446,11 +1446,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>momentum</t>
+          <t>bollinger</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-8.32</v>
+        <v>-7.52</v>
       </c>
     </row>
     <row r="70">
@@ -1461,11 +1461,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>vwma</t>
+          <t>momentum</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-8.67</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="71">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>rsi_macd</t>
+          <t>psar</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-10.79</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="72">
@@ -1491,11 +1491,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>inside_bar</t>
+          <t>vwma</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-10.9</v>
+        <v>-8.67</v>
       </c>
     </row>
     <row r="73">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>doji_reversal</t>
+          <t>rsi_macd</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-11.59</v>
+        <v>-10.79</v>
       </c>
     </row>
     <row r="74">
@@ -1521,11 +1521,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>vwap</t>
+          <t>inside_bar</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-12.49</v>
+        <v>-10.9</v>
       </c>
     </row>
     <row r="75">
@@ -1536,11 +1536,11 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>obv</t>
+          <t>vwap</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-13.82</v>
+        <v>-12.49</v>
       </c>
     </row>
     <row r="76">
@@ -1551,11 +1551,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>psar</t>
+          <t>obv</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-15.02</v>
+        <v>-13.82</v>
       </c>
     </row>
     <row r="77">
@@ -1566,11 +1566,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>zscore</t>
+          <t>mean_reversion</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-16.06</v>
+        <v>-15.15</v>
       </c>
     </row>
     <row r="78">
@@ -1581,11 +1581,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>adx</t>
+          <t>zscore</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-16.18</v>
+        <v>-16.06</v>
       </c>
     </row>
     <row r="79">
@@ -1596,11 +1596,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>pin_bar</t>
+          <t>adx</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-18.49</v>
+        <v>-16.18</v>
       </c>
     </row>
     <row r="80">
@@ -1611,11 +1611,11 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ad_line</t>
+          <t>pin_bar</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-20.67</v>
+        <v>-18.49</v>
       </c>
     </row>
     <row r="81">
@@ -1626,11 +1626,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>three_soldiers</t>
+          <t>ad_line</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-21.93</v>
+        <v>-20.67</v>
       </c>
     </row>
     <row r="82">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-24.09</v>
+        <v>-21.28</v>
       </c>
     </row>
     <row r="83">
@@ -1656,11 +1656,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>stoch_rsi</t>
+          <t>three_soldiers</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-24.69</v>
+        <v>-21.93</v>
       </c>
     </row>
     <row r="84">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-25.15</v>
+        <v>-23.24</v>
       </c>
     </row>
     <row r="85">
@@ -1686,11 +1686,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>klinger</t>
+          <t>stoch_rsi</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-27.41</v>
+        <v>-24.69</v>
       </c>
     </row>
     <row r="86">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-34.55</v>
+        <v>-26.08</v>
       </c>
     </row>
     <row r="87">
@@ -1716,11 +1716,11 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>heikin_ashi</t>
+          <t>klinger</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-37.29</v>
+        <v>-26.63</v>
       </c>
     </row>
     <row r="88">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>volatility_breakout</t>
+          <t>heikin_ashi</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-39.77</v>
+        <v>-36.02</v>
       </c>
     </row>
     <row r="89">
@@ -1746,11 +1746,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>rvi</t>
+          <t>volatility_breakout</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-46.26</v>
+        <v>-40.2</v>
       </c>
     </row>
     <row r="90">
@@ -1761,11 +1761,26 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
+          <t>rvi</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>-46.26</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>AKSA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>tema</t>
         </is>
       </c>
-      <c r="C90" t="n">
-        <v>-48.03</v>
+      <c r="C91" t="n">
+        <v>-46.76</v>
       </c>
     </row>
   </sheetData>

--- a/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
+++ b/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>41.53</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="9">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-20.67</v>
+        <v>-20.9</v>
       </c>
     </row>
     <row r="82">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-21.28</v>
+        <v>-21.51</v>
       </c>
     </row>
     <row r="83">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-46.76</v>
+        <v>-46.92</v>
       </c>
     </row>
   </sheetData>

--- a/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
+++ b/vbt_bist/output/AKSA/AKSA_Karsilastirma.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>69.94</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="3">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>55.24</v>
+        <v>56.12</v>
       </c>
     </row>
     <row r="4">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>47.38</v>
+        <v>48.21</v>
       </c>
     </row>
     <row r="5">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.69</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="6">
@@ -505,7 +505,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>44.51</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>43.82</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38.5</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="10">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36.8</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="11">
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>34.8</v>
+        <v>35.56</v>
       </c>
     </row>
     <row r="12">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>33.77</v>
+        <v>34.53</v>
       </c>
     </row>
     <row r="13">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.48</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="15">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30.15</v>
+        <v>30.89</v>
       </c>
     </row>
     <row r="16">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>29.04</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="17">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>26.91</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="19">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>26.66</v>
+        <v>27.38</v>
       </c>
     </row>
     <row r="20">
@@ -711,11 +711,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mfi</t>
+          <t>linreg</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>26.39</v>
+        <v>26.49</v>
       </c>
     </row>
     <row r="21">
@@ -726,11 +726,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>linreg</t>
+          <t>mfi</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.78</v>
+        <v>26.39</v>
       </c>
     </row>
     <row r="22">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.74</v>
+        <v>24.44</v>
       </c>
     </row>
     <row r="23">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="25">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.09</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="26">
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20.15</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="27">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.72</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="28">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.1</v>
+        <v>16.76</v>
       </c>
     </row>
     <row r="29">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14.23</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="30">
@@ -861,11 +861,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>historical_vol_rank</t>
+          <t>wma</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>13.35</v>
+        <v>13.82</v>
       </c>
     </row>
     <row r="31">
@@ -876,11 +876,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>wma</t>
+          <t>historical_vol_rank</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>13.17</v>
+        <v>13.35</v>
       </c>
     </row>
     <row r="32">
@@ -906,11 +906,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rainbow_ma</t>
+          <t>three_ma</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>10.73</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="34">
@@ -921,11 +921,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>three_ma</t>
+          <t>rainbow_ma</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>10.37</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="35">
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10.07</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="36">
@@ -951,11 +951,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>cmf</t>
+          <t>donchian</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8.98</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="37">
@@ -966,11 +966,11 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>donchian</t>
+          <t>fractal_breakout</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>8.130000000000001</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="38">
@@ -981,11 +981,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fractal_breakout</t>
+          <t>cmf</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>8.06</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="39">
@@ -996,11 +996,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>rsi</t>
+          <t>eom</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>8.039999999999999</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="40">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eom</t>
+          <t>rsi</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.46</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1026,11 +1026,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>natr</t>
+          <t>obv_ma</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7.33</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="42">
@@ -1041,11 +1041,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>obv_ma</t>
+          <t>natr</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="43">
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5.78</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="44">
@@ -1071,11 +1071,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>marubozu</t>
+          <t>dpo</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.5</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="45">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dpo</t>
+          <t>marubozu</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="46">
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.4</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="47">
@@ -1146,11 +1146,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>coppock</t>
+          <t>golden_cross</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="50">
@@ -1161,11 +1161,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>triple_screen</t>
+          <t>roc</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="51">
@@ -1176,11 +1176,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>golden_cross</t>
+          <t>coppock</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="52">
@@ -1191,11 +1191,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>roc</t>
+          <t>triple_screen</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="53">
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.53</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="54">
@@ -1266,11 +1266,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>connors_rsi</t>
+          <t>doji_reversal</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-0.78</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="58">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>connors_rsi</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-0.93</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="59">
@@ -1296,11 +1296,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>doji_reversal</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1.97</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="60">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-2.88</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="61">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-3.01</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="62">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-3.69</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="63">
@@ -1356,11 +1356,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ppo</t>
+          <t>stochastic</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-4.14</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="64">
@@ -1371,11 +1371,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>stochastic</t>
+          <t>tsi</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-4.36</v>
+        <v>-4.55</v>
       </c>
     </row>
     <row r="65">
@@ -1386,11 +1386,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>tsi</t>
+          <t>vpt</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-5.08</v>
+        <v>-4.74</v>
       </c>
     </row>
     <row r="66">
@@ -1401,11 +1401,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>vpt</t>
+          <t>ppo</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-5.28</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="67">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-8.32</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="71">
@@ -1480,7 +1480,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-8.4</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="72">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-8.67</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="73">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-10.79</v>
+        <v>-10.28</v>
       </c>
     </row>
     <row r="74">
@@ -1540,7 +1540,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-12.49</v>
+        <v>-11.99</v>
       </c>
     </row>
     <row r="76">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-13.82</v>
+        <v>-13.33</v>
       </c>
     </row>
     <row r="77">
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-20.9</v>
+        <v>-20.46</v>
       </c>
     </row>
     <row r="82">
@@ -1641,11 +1641,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>dema</t>
+          <t>three_soldiers</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-21.51</v>
+        <v>-21.48</v>
       </c>
     </row>
     <row r="83">
@@ -1656,11 +1656,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>three_soldiers</t>
+          <t>alma</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-21.93</v>
+        <v>-22.81</v>
       </c>
     </row>
     <row r="84">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>alma</t>
+          <t>dema</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-23.24</v>
+        <v>-22.92</v>
       </c>
     </row>
     <row r="85">
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-26.08</v>
+        <v>-25.89</v>
       </c>
     </row>
     <row r="87">
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-36.02</v>
+        <v>-36.97</v>
       </c>
     </row>
     <row r="89">
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-40.2</v>
+        <v>-40.04</v>
       </c>
     </row>
     <row r="90">
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-46.26</v>
+        <v>-46.42</v>
       </c>
     </row>
     <row r="91">
@@ -1780,7 +1780,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-46.92</v>
+        <v>-47.87</v>
       </c>
     </row>
   </sheetData>
